--- a/SraAccessionList.xlsx
+++ b/SraAccessionList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba589793935ecf89/Documents/Git_Hub/BINF_6210_Assignment_4/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba589793935ecf89/Documents/Git_Hub/BINF_6210_Assignment_4_Unofficial/FASTQ_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="8_{95DFE49D-1578-4EAD-83D5-EDA8B0BA1EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823B966D-D705-4BE4-9185-FE7A3BBA4726}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{95DFE49D-1578-4EAD-83D5-EDA8B0BA1EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF097F92-390B-4665-9FD1-8689266BAAB5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{0DC59907-BF0C-4F43-8019-53A3BA49EC0A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="59">
   <si>
     <t>SRR32497531</t>
   </si>
@@ -125,6 +125,78 @@
   </si>
   <si>
     <t>SRR25305921</t>
+  </si>
+  <si>
+    <t>print(sample.names) in R Studio results</t>
+  </si>
+  <si>
+    <t>[1] "SRR25305896"</t>
+  </si>
+  <si>
+    <t>[2] "SRR25305897"</t>
+  </si>
+  <si>
+    <t>[3] "SRR25305898"</t>
+  </si>
+  <si>
+    <t>[4] "SRR25305899"</t>
+  </si>
+  <si>
+    <t>[5] "SRR25305917"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [6] "SRR25305918"</t>
+  </si>
+  <si>
+    <t>[7] "SRR25305919"</t>
+  </si>
+  <si>
+    <t>[8] "SRR25305920"</t>
+  </si>
+  <si>
+    <t>[9] "SRR25305921"</t>
+  </si>
+  <si>
+    <t>[10] "SRR25374795"</t>
+  </si>
+  <si>
+    <t>[11] "SRR32497531"</t>
+  </si>
+  <si>
+    <t>[12] "SRR32497532"</t>
+  </si>
+  <si>
+    <t>[13] "SRR32497533"</t>
+  </si>
+  <si>
+    <t>[14]  "SRR32497534"</t>
+  </si>
+  <si>
+    <t>[15] "SRR32497535"</t>
+  </si>
+  <si>
+    <t>[16] "SRR32497540"</t>
+  </si>
+  <si>
+    <t>[17]  "SRR32497541"</t>
+  </si>
+  <si>
+    <t>[18] "SRR32497542"</t>
+  </si>
+  <si>
+    <t>[19]  "SRR32497543"</t>
+  </si>
+  <si>
+    <t>[20]  "SRR32497544"</t>
+  </si>
+  <si>
+    <t>Tumor</t>
+  </si>
+  <si>
+    <t>Study 2</t>
+  </si>
+  <si>
+    <t>Study 1</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2616AB6E-DC30-4514-96D3-26BB4E65A3F7}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="18.73046875" customWidth="1"/>
@@ -1008,7 +1080,7 @@
     <col min="8" max="8" width="14.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1030,8 +1102,11 @@
       <c r="G1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1053,8 +1128,17 @@
       <c r="G2" s="1">
         <v>45989</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1076,8 +1160,17 @@
       <c r="G3" s="1">
         <v>45989</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1099,8 +1192,17 @@
       <c r="G4" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1224,17 @@
       <c r="G5" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1145,8 +1256,17 @@
       <c r="G6" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1168,8 +1288,17 @@
       <c r="G7" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1191,8 +1320,17 @@
       <c r="G8" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1214,8 +1352,17 @@
       <c r="G9" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1237,8 +1384,17 @@
       <c r="G10" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1260,8 +1416,17 @@
       <c r="G11" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1280,8 +1445,17 @@
       <c r="G12" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1300,8 +1474,17 @@
       <c r="G13" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1320,8 +1503,17 @@
       <c r="G14" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1340,8 +1532,17 @@
       <c r="G15" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1360,8 +1561,17 @@
       <c r="G16" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1380,8 +1590,17 @@
       <c r="G17" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1400,8 +1619,17 @@
       <c r="G18" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1420,8 +1648,17 @@
       <c r="G19" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1440,8 +1677,17 @@
       <c r="G20" s="1">
         <v>45992</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1459,6 +1705,15 @@
       </c>
       <c r="G21" s="1">
         <v>45992</v>
+      </c>
+      <c r="I21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
